--- a/ci-cd-merge-resolver/repoCollector/datasets/tika.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/tika.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -62,6 +62,42 @@
     <t>c95ede6c26313d970ad1a867bdb6ef730f90abba</t>
   </si>
   <si>
+    <t>7ca6597c5652ab8850bb8ce3d48d602188f5bdbf</t>
+  </si>
+  <si>
+    <t>beedc4277526c6327524acb3a799b2ca6c898a05</t>
+  </si>
+  <si>
+    <t>a8aa2fc017262d961918085cf221c226b2979201</t>
+  </si>
+  <si>
+    <t>b5f5403fb150f2a290fe1cfa10a6fe572b1dd50a</t>
+  </si>
+  <si>
+    <t>33da38ebb209250680aee3ab8565c89846f3a865</t>
+  </si>
+  <si>
+    <t>96a3502de309df863fcf37897466766e62d4e9a7</t>
+  </si>
+  <si>
+    <t>e147de3429b775f5036c78b18a1cb688971be0af</t>
+  </si>
+  <si>
+    <t>0dbd69cef5ec603a11d7f5b52f119e3bea1550b5</t>
+  </si>
+  <si>
+    <t>cdb684d9c1b0ebb01a783180f07417760fa04d6f</t>
+  </si>
+  <si>
+    <t>e780d56652d48dd0f50b4e62a58153e95f055022</t>
+  </si>
+  <si>
+    <t>0d69ca7540b4350e043c5b9ed34d14a46bd70cf7</t>
+  </si>
+  <si>
+    <t>bb46c0e0c2f572e58b847ef59d7e8809326c3da4</t>
+  </si>
+  <si>
     <t>fed63cdcf644e07aa810a03cf6809ccba984c62f</t>
   </si>
   <si>
@@ -71,6 +107,15 @@
     <t>6114fac007291b3f80e202f0f4b17411bbb6d12d</t>
   </si>
   <si>
+    <t>7805990a015c12a9ba337163f11994b9a307b01d</t>
+  </si>
+  <si>
+    <t>b7221e4d19e82fccdec96ac48feed829fc789e89</t>
+  </si>
+  <si>
+    <t>0220d570780ecd9f0ebf56f99262ee23fa318f83</t>
+  </si>
+  <si>
     <t>04ce661e8eb44872c75727a3f0fcb2587ea92ad6</t>
   </si>
   <si>
@@ -80,6 +125,15 @@
     <t>c53f73c65d249df825c6df0f1bee6e7456260531</t>
   </si>
   <si>
+    <t>0745b913bfafd32b25031c89a56b653b5dd3e460</t>
+  </si>
+  <si>
+    <t>219338f0925ef55a4748906e14a757a05b94ce35</t>
+  </si>
+  <si>
+    <t>618345263ee41108e1a225dbcdbb8db16b2aae28</t>
+  </si>
+  <si>
     <t>58784b784c4af74d8f60aa8f3e0a177ca3258545</t>
   </si>
   <si>
@@ -89,24 +143,6 @@
     <t>17f2d104d2b36c2c7e5511100073449e430dd05f</t>
   </si>
   <si>
-    <t>7805990a015c12a9ba337163f11994b9a307b01d</t>
-  </si>
-  <si>
-    <t>b7221e4d19e82fccdec96ac48feed829fc789e89</t>
-  </si>
-  <si>
-    <t>0220d570780ecd9f0ebf56f99262ee23fa318f83</t>
-  </si>
-  <si>
-    <t>0745b913bfafd32b25031c89a56b653b5dd3e460</t>
-  </si>
-  <si>
-    <t>219338f0925ef55a4748906e14a757a05b94ce35</t>
-  </si>
-  <si>
-    <t>618345263ee41108e1a225dbcdbb8db16b2aae28</t>
-  </si>
-  <si>
     <t>db392986f204deca584c16439d2d075d589218c8</t>
   </si>
   <si>
@@ -116,6 +152,15 @@
     <t>d21a66fb789b1fe00e522bcd37bcd6373c4e09ed</t>
   </si>
   <si>
+    <t>ba9fdc1b507ea85fb261912a890d8eb45514d031</t>
+  </si>
+  <si>
+    <t>fc19baf5f1ac57084dc8915cd20bb36a65b3e275</t>
+  </si>
+  <si>
+    <t>91d389f0687b987083c63dc3b4683e90a0a897ab</t>
+  </si>
+  <si>
     <t>79781050f460133ebe8c1a305a4c72841ebfc0b3</t>
   </si>
   <si>
@@ -123,15 +168,6 @@
   </si>
   <si>
     <t>3fa217103b38f18bb0904729b9068f52bdd6b08a</t>
-  </si>
-  <si>
-    <t>ba9fdc1b507ea85fb261912a890d8eb45514d031</t>
-  </si>
-  <si>
-    <t>fc19baf5f1ac57084dc8915cd20bb36a65b3e275</t>
-  </si>
-  <si>
-    <t>91d389f0687b987083c63dc3b4683e90a0a897ab</t>
   </si>
 </sst>
 </file>
@@ -176,7 +212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -222,7 +258,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>253.0</v>
+        <v>256.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>2.0</v>
@@ -237,10 +273,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>36.81898880004883</v>
+        <v>39.1829948425293</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -269,10 +305,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>41.340003967285156</v>
+        <v>43.16701126098633</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -286,7 +322,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>1256.0</v>
+        <v>238.0</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>1.0</v>
@@ -301,10 +337,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>192.98802185058594</v>
+        <v>23.195995330810547</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -318,7 +354,7 @@
         <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>1549.0</v>
+        <v>238.0</v>
       </c>
       <c r="E5" t="n" s="0">
         <v>1.0</v>
@@ -333,10 +369,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>266.4389953613281</v>
+        <v>23.54999351501465</v>
       </c>
       <c r="J5" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -350,13 +386,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>1531.0</v>
+        <v>173.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G6" t="b" s="0">
         <v>0</v>
@@ -365,10 +401,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>250.44100952148438</v>
+        <v>7.302999019622803</v>
       </c>
       <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -382,7 +418,7 @@
         <v>27</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>1560.0</v>
+        <v>203.0</v>
       </c>
       <c r="E7" t="n" s="0">
         <v>2.0</v>
@@ -397,10 +433,10 @@
         <v>1</v>
       </c>
       <c r="I7" t="n" s="0">
-        <v>279.7010192871094</v>
+        <v>12.881003379821777</v>
       </c>
       <c r="J7" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -414,7 +450,7 @@
         <v>30</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>1665.0</v>
+        <v>1386.0</v>
       </c>
       <c r="E8" t="n" s="0">
         <v>1.0</v>
@@ -429,10 +465,10 @@
         <v>1</v>
       </c>
       <c r="I8" t="n" s="0">
-        <v>421.10028076171875</v>
+        <v>356.57305908203125</v>
       </c>
       <c r="J8" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -446,13 +482,13 @@
         <v>33</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>2090.0</v>
+        <v>1715.0</v>
       </c>
       <c r="E9" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F9" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G9" t="b" s="0">
         <v>0</v>
@@ -461,10 +497,10 @@
         <v>1</v>
       </c>
       <c r="I9" t="n" s="0">
-        <v>899.0342407226562</v>
+        <v>442.3499755859375</v>
       </c>
       <c r="J9" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -478,7 +514,7 @@
         <v>36</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>1799.0</v>
+        <v>1715.0</v>
       </c>
       <c r="E10" t="n" s="0">
         <v>1.0</v>
@@ -493,10 +529,10 @@
         <v>1</v>
       </c>
       <c r="I10" t="n" s="0">
-        <v>588.3480224609375</v>
+        <v>443.3983154296875</v>
       </c>
       <c r="J10" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -510,7 +546,7 @@
         <v>39</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>1824.0</v>
+        <v>1826.0</v>
       </c>
       <c r="E11" t="n" s="0">
         <v>1.0</v>
@@ -525,10 +561,138 @@
         <v>1</v>
       </c>
       <c r="I11" t="n" s="0">
-        <v>910.405029296875</v>
+        <v>461.9089660644531</v>
       </c>
       <c r="J11" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="D12" t="n" s="0">
+        <v>1757.0</v>
+      </c>
+      <c r="E12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G12" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>483.0649719238281</v>
+      </c>
+      <c r="J12" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D13" t="n" s="0">
+        <v>1999.0</v>
+      </c>
+      <c r="E13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G13" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>891.676025390625</v>
+      </c>
+      <c r="J13" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="D14" t="n" s="0">
+        <v>1863.0</v>
+      </c>
+      <c r="E14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G14" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>672.0880737304688</v>
+      </c>
+      <c r="J14" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="D15" t="n" s="0">
+        <v>1875.0</v>
+      </c>
+      <c r="E15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F15" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G15" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>659.5391235351562</v>
+      </c>
+      <c r="J15" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
